--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/MOTOR DE PARTIDA - 19_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/MOTOR DE PARTIDA - 19_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,11 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,11 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,7 +564,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MOTOR PARTIDA BURGMAN 125</t>
+          <t>MOTOR PARTIDA IRON BURGMAN 125</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -599,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -620,7 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -662,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -687,7 +652,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -708,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -733,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -754,7 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -775,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -796,11 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -821,11 +772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -846,53 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>6121-K62-305</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MOTOR PARTIDA HONDA POP110 2016/ BIZ110 2016</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>06121-KVS-305</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MOTOR PARTIDA HONDA TITAN FAN160 2015</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
